--- a/src/main/resources/excel/website-terminal-code-exceldown.xlsx
+++ b/src/main/resources/excel/website-terminal-code-exceldown.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmm11199317\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace_kc_logix\kc.logix\src\main\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4100B6-E56A-4749-A955-21B5090BF221}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8728E6F9-EC7F-460F-A436-6DCB906FFD0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>F/T</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -30,27 +30,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매출</t>
-  </si>
-  <si>
-    <t>이월 매출</t>
-  </si>
-  <si>
-    <t>INVOICE</t>
-  </si>
-  <si>
-    <t>CNEE</t>
-  </si>
-  <si>
-    <t>PROFIT DATE</t>
-  </si>
-  <si>
-    <t>국내매출</t>
-  </si>
-  <si>
-    <t>해외매출</t>
-  </si>
-  <si>
     <t>Q'ty</t>
   </si>
   <si>
@@ -82,41 +61,22 @@
     <t>POL</t>
   </si>
   <si>
-    <t>Terminal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ETD</t>
   </si>
   <si>
     <t>ETA</t>
   </si>
   <si>
-    <t>ATA</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
     <t>DEM RATE</t>
   </si>
   <si>
     <t>END OF F/T</t>
   </si>
   <si>
-    <t>ESTIMATE RETURN DATE</t>
-  </si>
-  <si>
     <t>RETURN DATE</t>
   </si>
   <si>
     <t>TOTAL DEM</t>
-  </si>
-  <si>
-    <t>DEM RECEIVED</t>
-  </si>
-  <si>
-    <t>DEM RCVD</t>
   </si>
   <si>
     <t>COMMISSION DEM</t>
@@ -129,23 +89,7 @@
     <t>DEPOT IN DATE(REPO ONLY)</t>
   </si>
   <si>
-    <t>REPOSITION 매입</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
     <t>POD</t>
-  </si>
-  <si>
-    <t>A/N&amp;EDI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -188,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -224,48 +168,32 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,290 +510,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" customWidth="1"/>
-    <col min="10" max="10" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.625" customWidth="1"/>
-    <col min="14" max="14" width="11.5" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
-    <col min="16" max="16" width="26.375" customWidth="1"/>
-    <col min="17" max="17" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.625" customWidth="1"/>
+    <col min="7" max="7" width="26.375" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
+    <col min="12" max="13" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
-    <col min="19" max="19" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.5" customWidth="1"/>
-    <col min="22" max="22" width="23.25" customWidth="1"/>
-    <col min="23" max="24" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.375" customWidth="1"/>
-    <col min="26" max="26" width="20.125" customWidth="1"/>
-    <col min="27" max="27" width="4.125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15" customWidth="1"/>
-    <col min="30" max="30" width="20" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5" customWidth="1"/>
-    <col min="32" max="32" width="23" customWidth="1"/>
-    <col min="33" max="33" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>10</v>
+      <c r="J1" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3" t="s">
+      <c r="N1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="R1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="W1" s="6"/>
     </row>
-    <row r="2" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-    </row>
-    <row r="3" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
+    <row r="2" spans="1:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AC1:AC2"/>
-    <mergeCell ref="AD1:AD2"/>
-    <mergeCell ref="AE1:AE2"/>
-    <mergeCell ref="AF1:AF2"/>
-    <mergeCell ref="AG1:AG2"/>
-    <mergeCell ref="AH1:AH2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
